--- a/data/fmsForecastOutput/File1/RPT_RPT8270621607594XL_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8270621607594XL_fmsForecastOutput.xlsx
@@ -1875,46 +1875,46 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>216.133465228332</v>
+        <v>216.1334652283319</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>243.9667551291313</v>
+        <v>243.9667551291312</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>275.4001197158068</v>
+        <v>275.4001197158067</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>298.5089243363708</v>
+        <v>298.5089243363707</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>317.6553552581551</v>
+        <v>317.6553552581549</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>39.81339560726499</v>
+        <v>39.81339560726497</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>43.23244220626533</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>47.89461068103476</v>
+        <v>47.89461068103474</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>54.07187906873418</v>
+        <v>54.07187906873415</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>58.8270571155403</v>
+        <v>58.82705711554027</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>11775245.61338573</v>
+        <v>11775245.61338572</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>12951571.06665268</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>14529409.26621108</v>
+        <v>14529409.26621107</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>16617237.82976372</v>
+        <v>16617237.82976371</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>18393072.45273897</v>
@@ -1925,46 +1925,46 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>265.869498314593</v>
+        <v>265.8694983145929</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>300.1077076291592</v>
+        <v>300.1077076291591</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>338.7744308234145</v>
+        <v>338.7744308234143</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>367.2009694190392</v>
+        <v>367.200969419039</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>390.7533238788728</v>
+        <v>390.7533238788726</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>49.39925786435096</v>
+        <v>49.39925786435095</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.64549440228228</v>
+        <v>53.64549440228227</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>59.43268232428613</v>
+        <v>59.43268232428611</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>67.09293788255476</v>
+        <v>67.09293788255474</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>72.99007194932518</v>
+        <v>72.99007194932516</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>11775245.61338573</v>
+        <v>11775245.61338572</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>12951571.06665268</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>14529409.26621108</v>
+        <v>14529409.26621107</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>16617237.82976372</v>
+        <v>16617237.82976371</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>18393072.45273897</v>
@@ -2031,7 +2031,7 @@
         <v>401.2860412850874</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>431.9307316239914</v>
+        <v>431.9307316239913</v>
       </c>
       <c r="G9" s="157" t="n">
         <v>448.0049619414276</v>
@@ -2052,16 +2052,16 @@
         <v>29.58163533805692</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>6593767.945674588</v>
+        <v>6593767.945674586</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>5995429.771478219</v>
+        <v>5995429.771478218</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>6580069.091165541</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>7474270.121441578</v>
+        <v>7474270.121441577</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>8285795.383143709</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>351.6771583083325</v>
+        <v>351.6771583083324</v>
       </c>
       <c r="U9" s="156" t="n">
         <v>392.0022100735026</v>
@@ -2081,7 +2081,7 @@
         <v>477.3577937241033</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>513.8117947720614</v>
+        <v>513.8117947720613</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>532.9332152320696</v>
@@ -2090,7 +2090,7 @@
         <v>25.41710559099167</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>22.87903949306706</v>
+        <v>22.87903949306705</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>24.8941476968138</v>
@@ -2102,16 +2102,16 @@
         <v>30.87254372319671</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>6593767.945674588</v>
+        <v>6593767.945674586</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>5995429.771478219</v>
+        <v>5995429.771478218</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>6580069.091165541</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>7474270.121441578</v>
+        <v>7474270.121441577</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>8285795.383143709</v>
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>239.2259865129068</v>
+        <v>239.2259865129067</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>265.8065226600866</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>305.2491728116328</v>
+        <v>305.2491728116327</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>330.1481935878891</v>
+        <v>330.148193587889</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>349.2113647928791</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>32.39223937934148</v>
+        <v>32.39223937934147</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>33.06158192789842</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>36.45964040531643</v>
+        <v>36.45964040531642</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>41.19276042549243</v>
+        <v>41.19276042549242</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>45.00766351011699</v>
+        <v>45.00766351011698</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>18369013.55906032</v>
+        <v>18369013.55906031</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>18947000.8381309</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>21109478.35737662</v>
+        <v>21109478.35737661</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>24091507.95120529</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>26678867.83588269</v>
+        <v>26678867.83588268</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>291.3909762142909</v>
+        <v>291.3909762142908</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>324.1530504819149</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>372.4818196483732</v>
+        <v>372.4818196483731</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>402.8646296146745</v>
+        <v>402.8646296146744</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>426.0552249633644</v>
+        <v>426.0552249633643</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>36.90103134339891</v>
@@ -2241,28 +2241,28 @@
         <v>37.6322404785754</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>41.4895481920368</v>
+        <v>41.48954819203679</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>46.89533929218953</v>
+        <v>46.89533929218952</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>51.2679157664497</v>
+        <v>51.26791576644969</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>18369013.55906032</v>
+        <v>18369013.55906031</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>18947000.8381309</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>21109478.35737662</v>
+        <v>21109478.35737661</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>24091507.95120529</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>26678867.83588269</v>
+        <v>26678867.83588268</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2467,13 +2467,13 @@
         <v>267.2672358731453</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>306.9337740175904</v>
+        <v>306.9337740175903</v>
       </c>
       <c r="F12" s="162" t="n">
         <v>332.0494079649318</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>351.3712539359111</v>
+        <v>351.371253935911</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>32.4821909150474</v>
@@ -2482,28 +2482,28 @@
         <v>33.14218811819336</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>36.54901128631239</v>
+        <v>36.54901128631238</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>41.30932249399222</v>
+        <v>41.30932249399221</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>45.16608955912068</v>
+        <v>45.16608955912066</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>18558306.81913976</v>
+        <v>18558306.81913975</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>19135734.65352813</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>21319985.29902064</v>
+        <v>21319985.29902063</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>24340860.77391468</v>
+        <v>24340860.77391467</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>26973354.06855896</v>
+        <v>26973354.06855895</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>292.7479908271904</v>
+        <v>292.7479908271903</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>325.657399901275</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>374.218834337951</v>
+        <v>374.2188343379509</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>404.8293413707548</v>
+        <v>404.8293413707547</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>428.2938237558373</v>
+        <v>428.2938237558371</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>36.96996275410194</v>
@@ -2532,28 +2532,28 @@
         <v>37.69004096065451</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>41.55390968080607</v>
+        <v>41.55390968080606</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>46.98568774798557</v>
+        <v>46.98568774798555</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>51.40186937097265</v>
+        <v>51.40186937097263</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>18558306.81913976</v>
+        <v>18558306.81913975</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>19135734.65352813</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>21319985.29902064</v>
+        <v>21319985.29902063</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>24340860.77391468</v>
+        <v>24340860.77391467</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>26973354.06855896</v>
+        <v>26973354.06855895</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>947.8591485462172</v>
+        <v>947.8591485462167</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>966.8146387551301</v>
+        <v>966.8146387551299</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>846.9588199382875</v>
+        <v>846.9588199382874</v>
       </c>
       <c r="F13" s="156" t="n">
         <v>874.9131918259557</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>912.1028898581557</v>
+        <v>912.1028898581553</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>829.3350195536839</v>
+        <v>829.3350195536834</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>851.119248541606</v>
+        <v>851.1192485416059</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>746.2435640328197</v>
+        <v>746.2435640328196</v>
       </c>
       <c r="K13" s="156" t="n">
         <v>776.1142954230249</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>816.4013968752946</v>
+        <v>816.4013968752944</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>7641214.656498311</v>
+        <v>7641214.656498308</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>8787875.696365627</v>
+        <v>8787875.696365625</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8681680.728870433</v>
+        <v>8681680.728870431</v>
       </c>
       <c r="P13" s="159" t="n">
         <v>10162681.59710787</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>12084613.03805428</v>
+        <v>12084613.03805427</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,25 +2653,25 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>618.5905654383046</v>
+        <v>618.5905654383043</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>630.9612720189984</v>
+        <v>630.9612720189983</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>552.7411283967137</v>
+        <v>552.7411283967136</v>
       </c>
       <c r="W13" s="156" t="n">
         <v>570.9846730615382</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>595.2553638804247</v>
+        <v>595.2553638804245</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>543.7347312224258</v>
+        <v>543.7347312224257</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>557.9064574414627</v>
+        <v>557.9064574414626</v>
       </c>
       <c r="AA13" s="156" t="n">
         <v>489.1471491792705</v>
@@ -2680,22 +2680,22 @@
         <v>508.6144986392009</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>534.8583376259369</v>
+        <v>534.8583376259367</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>7641214.656498311</v>
+        <v>7641214.656498308</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>8787875.696365627</v>
+        <v>8787875.696365625</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8681680.728870433</v>
+        <v>8681680.728870431</v>
       </c>
       <c r="AG13" s="159" t="n">
         <v>10162681.59710787</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>12084613.03805428</v>
+        <v>12084613.03805427</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,46 +2746,46 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>307.472901030977</v>
+        <v>307.4729010309769</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>346.0720602558285</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>376.377634168829</v>
+        <v>376.3776341688289</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>406.3036485831515</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>433.9043987089516</v>
+        <v>433.9043987089515</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>45.12867240894705</v>
+        <v>45.12867240894703</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>47.51272469690297</v>
+        <v>47.51272469690296</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>50.42637895446828</v>
+        <v>50.42637895446826</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>57.28360595425107</v>
+        <v>57.28360595425106</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>63.81958668865224</v>
+        <v>63.81958668865223</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>26199521.47563807</v>
+        <v>26199521.47563806</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>27923610.34989376</v>
+        <v>27923610.34989375</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>30001666.02789107</v>
+        <v>30001666.02789106</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>34503542.37102255</v>
+        <v>34503542.37102254</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>39057967.10661323</v>
@@ -2796,46 +2796,46 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>345.886185335095</v>
+        <v>345.8861853350948</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>384.1566502760281</v>
+        <v>384.156650276028</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>412.799359127015</v>
+        <v>412.7993591270148</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>442.7803004622236</v>
+        <v>442.7803004622235</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>468.9947424244635</v>
+        <v>468.9947424244633</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>50.77066701841001</v>
+        <v>50.77066701840999</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>53.34381563760422</v>
+        <v>53.34381563760421</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>56.51982287673963</v>
+        <v>56.51982287673961</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>64.12945990411419</v>
+        <v>64.12945990411417</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>71.35851346967662</v>
+        <v>71.35851346967661</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>26199521.47563807</v>
+        <v>26199521.47563806</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>27923610.34989376</v>
+        <v>27923610.34989375</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>30001666.02789107</v>
+        <v>30001666.02789106</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>34503542.37102255</v>
+        <v>34503542.37102254</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>39057967.10661323</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="C24" s="79" t="n">
-        <v>8061.550778106699</v>
+        <v>8061.5507781067</v>
       </c>
       <c r="D24" s="80" t="n">
         <v>9089.514519226654</v>
@@ -3870,7 +3870,7 @@
         <v>1553.115988492877</v>
       </c>
       <c r="M24" s="79" t="n">
-        <v>9213.664534038991</v>
+        <v>9213.664534038993</v>
       </c>
       <c r="N24" s="80" t="n">
         <v>10325.08160451507</v>
@@ -3932,7 +3932,7 @@
         <v>19981.10872635</v>
       </c>
       <c r="AH24" s="81" t="n">
-        <v>22594.04441874078</v>
+        <v>22594.04441874079</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>75746.07656057712</v>
+        <v>75746.07656057713</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>72688.08266062764</v>
@@ -4004,7 +4004,7 @@
         <v>77924.74582767999</v>
       </c>
       <c r="X25" s="93" t="n">
-        <v>83280.18114809449</v>
+        <v>83280.1811480945</v>
       </c>
       <c r="Y25" s="91" t="n">
         <v>440290.5054708906</v>
@@ -4022,7 +4022,7 @@
         <v>464068.2038937364</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>516036.5820314677</v>
+        <v>516036.5820314678</v>
       </c>
       <c r="AE25" s="92" t="n">
         <v>523464.8106088847</v>
@@ -4408,34 +4408,34 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>221.0360737948077</v>
+        <v>221.0360737948076</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>256.0373391449633</v>
+        <v>256.0373391449632</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>290.7627916682948</v>
+        <v>290.7627916682947</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>319.991144795821</v>
+        <v>319.9911447958209</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>341.4154535024091</v>
+        <v>341.415453502409</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>40.716492655001</v>
+        <v>40.71649265500098</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>45.37142555087766</v>
+        <v>45.37142555087765</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>50.56632045713852</v>
+        <v>50.5663204571385</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>57.96316650475859</v>
+        <v>57.96316650475856</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>63.22722425690537</v>
+        <v>63.22722425690534</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>12042346.40666432</v>
@@ -4444,7 +4444,7 @@
         <v>13592367.50063526</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>15339904.73168357</v>
+        <v>15339904.73168356</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>17813098.7819269</v>
@@ -4458,34 +4458,34 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>271.900281555979</v>
+        <v>271.9002815559789</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>314.9559409338122</v>
+        <v>314.9559409338121</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>357.6723182026996</v>
+        <v>357.6723182026994</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>393.6266188213828</v>
+        <v>393.6266188213826</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>419.981029979044</v>
+        <v>419.9810299790439</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>50.51979338404686</v>
+        <v>50.51979338404685</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>56.2996775384676</v>
+        <v>56.29967753846758</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>62.74802148516463</v>
+        <v>62.74802148516461</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>71.92128693801257</v>
+        <v>71.92128693801254</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>78.44960931163953</v>
+        <v>78.44960931163951</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>12042346.40666432</v>
@@ -4494,7 +4494,7 @@
         <v>13592367.50063526</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>15339904.73168357</v>
+        <v>15339904.73168356</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>17813098.7819269</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>300.077895273195</v>
+        <v>300.0778952731949</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>344.5819267028969</v>
@@ -4525,7 +4525,7 @@
         <v>481.6271647332809</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>24.667889004872</v>
+        <v>24.66788900487199</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>22.92204977440284</v>
@@ -4540,10 +4540,10 @@
         <v>31.8016994595361</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>6692886.60570795</v>
+        <v>6692886.605707948</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>6269230.880298923</v>
+        <v>6269230.880298922</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>6914963.558694161</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>356.9636301682845</v>
+        <v>356.9636301682843</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>409.9042861329855</v>
@@ -4569,16 +4569,16 @@
         <v>501.6530529280691</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>551.0285088812948</v>
+        <v>551.0285088812947</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>572.929175454023</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>25.7991799176683</v>
+        <v>25.79917991766829</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>23.92388642159841</v>
+        <v>23.9238864215984</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>26.1611423471734</v>
@@ -4590,10 +4590,10 @@
         <v>33.18948887769566</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>6692886.60570795</v>
+        <v>6692886.605707948</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>6269230.880298923</v>
+        <v>6269230.880298922</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>6914963.558694161</v>
@@ -4618,28 +4618,28 @@
         <v>278.6373656290039</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>321.8118430811794</v>
+        <v>321.8118430811793</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>353.955220732701</v>
+        <v>353.9552207327009</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>375.3589552057338</v>
+        <v>375.3589552057337</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>33.03803716042054</v>
+        <v>33.03803716042053</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>34.65750952882992</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>38.43792259562441</v>
+        <v>38.4379225956244</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>44.16317548353626</v>
+        <v>44.16317548353624</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>48.37766251229758</v>
+        <v>48.37766251229757</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>18735233.01237227</v>
@@ -4648,13 +4648,13 @@
         <v>19861598.38093419</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>22254868.29037773</v>
+        <v>22254868.29037772</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>25828749.574492</v>
+        <v>25828749.57449199</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>28676477.81992513</v>
+        <v>28676477.81992512</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4668,28 +4668,28 @@
         <v>339.8003598368765</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>392.6925003306882</v>
+        <v>392.6925003306881</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>431.9152479709064</v>
+        <v>431.9152479709063</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>457.9565851101229</v>
+        <v>457.9565851101228</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>37.63672003358236</v>
+        <v>37.63672003358235</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>39.44879999456067</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>43.740750709664</v>
+        <v>43.74075070966398</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>50.27696801885743</v>
+        <v>50.27696801885742</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>55.10665813835661</v>
+        <v>55.10665813835659</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>18735233.01237227</v>
@@ -4698,13 +4698,13 @@
         <v>19861598.38093419</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>22254868.29037773</v>
+        <v>22254868.29037772</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>25828749.574492</v>
+        <v>25828749.57449199</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>28676477.81992513</v>
+        <v>28676477.81992512</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4822,31 +4822,31 @@
         <v>280.1707897473391</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>323.5902174771212</v>
+        <v>323.5902174771211</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>355.9851761636973</v>
+        <v>355.9851761636972</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>377.6702160634011</v>
+        <v>377.670216063401</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>33.12913358718164</v>
+        <v>33.12913358718163</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>34.74227953416757</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>38.53242462015204</v>
+        <v>38.53242462015203</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>44.28710334210224</v>
+        <v>44.28710334210223</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>48.54662016729271</v>
+        <v>48.5466201672927</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>18927929.68833789</v>
+        <v>18927929.68833788</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>20059600.17044197</v>
@@ -4858,7 +4858,7 @@
         <v>26095470.74239375</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>28992219.326187</v>
+        <v>28992219.32618699</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,19 +4866,19 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>298.5786063772005</v>
+        <v>298.5786063772004</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>341.3800072400603</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>394.5266511482455</v>
+        <v>394.5266511482454</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>434.0114481376268</v>
+        <v>434.0114481376266</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>460.3501827329069</v>
+        <v>460.3501827329068</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>37.70628766997336</v>
@@ -4887,16 +4887,16 @@
         <v>39.50970086946282</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>43.80892495026002</v>
+        <v>43.80892495026001</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>50.37264915679533</v>
+        <v>50.37264915679532</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>55.24912722353439</v>
+        <v>55.24912722353437</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>18927929.68833789</v>
+        <v>18927929.68833788</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>20059600.17044197</v>
@@ -4908,7 +4908,7 @@
         <v>26095470.74239375</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>28992219.326187</v>
+        <v>28992219.32618699</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,43 +4918,43 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>921.4658679731419</v>
+        <v>921.4658679731416</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>951.5996717218443</v>
+        <v>951.5996717218441</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>879.1789239242275</v>
+        <v>879.1789239242274</v>
       </c>
       <c r="F40" s="156" t="n">
         <v>918.7940300041739</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>959.4808656089658</v>
+        <v>959.4808656089655</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>806.2420611814094</v>
+        <v>806.2420611814091</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>837.7250044033194</v>
+        <v>837.7250044033193</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>774.6322467715247</v>
+        <v>774.6322467715246</v>
       </c>
       <c r="K40" s="156" t="n">
         <v>815.0399238435808</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>858.8082854118504</v>
+        <v>858.8082854118502</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>7428443.884957647</v>
+        <v>7428443.884957645</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>8649579.032607021</v>
+        <v>8649579.032607019</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>9011950.216916285</v>
+        <v>9011950.216916284</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>10672385.86352629</v>
@@ -4968,43 +4968,43 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>601.3658180921282</v>
+        <v>601.3658180921279</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>621.0317006531675</v>
+        <v>621.0317006531674</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>573.7685694186346</v>
+        <v>573.7685694186345</v>
       </c>
       <c r="W40" s="156" t="n">
         <v>599.6221267825931</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>626.1751148307285</v>
+        <v>626.1751148307283</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>528.5943558401868</v>
+        <v>528.5943558401867</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>549.1265651877015</v>
+        <v>549.1265651877014</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>507.7553407937467</v>
+        <v>507.7553407937466</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>534.1238071264847</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>562.6408450951338</v>
+        <v>562.6408450951336</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>7428443.884957647</v>
+        <v>7428443.884957645</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>8649579.032607021</v>
+        <v>8649579.032607019</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>9011950.216916285</v>
+        <v>9011950.216916284</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>10672385.86352629</v>
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>309.3136892127146</v>
+        <v>309.3136892127145</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>355.8080302137848</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>395.0354675142579</v>
+        <v>395.0354675142578</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>432.9675524016264</v>
+        <v>432.9675524016263</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>463.3059453378227</v>
+        <v>463.3059453378225</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>45.39885012720889</v>
+        <v>45.39885012720887</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>48.84938984094185</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>52.9261209405287</v>
+        <v>52.92612094052869</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>61.04287458219935</v>
+        <v>61.04287458219934</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>68.14402902997155</v>
+        <v>68.14402902997153</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>26356373.57329554</v>
+        <v>26356373.57329553</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>28709179.20304899</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>31488911.90547825</v>
+        <v>31488911.90547824</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>36767856.60592004</v>
+        <v>36767856.60592003</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>41704551.57206431</v>
+        <v>41704551.5720643</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>347.9569473438972</v>
+        <v>347.956947343897</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>394.9640457169419</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>433.2626942151909</v>
+        <v>433.2626942151908</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>471.8380049288472</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>500.7740256700743</v>
+        <v>500.7740256700741</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>51.07462240281317</v>
+        <v>51.07462240281316</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>54.84452559409867</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>59.32162973297365</v>
+        <v>59.32162973297363</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>68.33799152025125</v>
+        <v>68.33799152025124</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>76.1937966965538</v>
+        <v>76.19379669655378</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>26356373.57329554</v>
+        <v>26356373.57329553</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>28709179.20304899</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>31488911.90547825</v>
+        <v>31488911.90547824</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>36767856.60592004</v>
+        <v>36767856.60592003</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>41704551.57206431</v>
+        <v>41704551.5720643</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.448222479721036</v>
+        <v>0.4482224797210358</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.0661734850564291</v>
+        <v>0.06617348505642909</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.05246753533845386</v>
+        <v>0.05246753533845384</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.03611980663748068</v>
+        <v>0.03611980663748066</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.02151480147994134</v>
+        <v>0.02151480147994133</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.08256592234039495</v>
+        <v>0.08256592234039492</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.01172635741609546</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.009124586369177422</v>
+        <v>0.009124586369177418</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.006542738448540089</v>
+        <v>0.006542738448540086</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.003984357368889431</v>
+        <v>0.003984357368889429</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>24419.77128613649</v>
+        <v>24419.77128613648</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>3512.981078027557</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2768.053604727735</v>
+        <v>2768.053604727734</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>2010.698402382618</v>
+        <v>2010.698402382617</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1245.763044370075</v>
+        <v>1245.763044370074</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,19 +6384,19 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.5513661926016877</v>
+        <v>0.5513661926016875</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.0814011437566808</v>
+        <v>0.08140114375668078</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.0645412189338707</v>
+        <v>0.06454121893387069</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.04443159628140853</v>
+        <v>0.04443159628140851</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.0264657278768334</v>
+        <v>0.02646572787683339</v>
       </c>
       <c r="Y57" s="148" t="n">
         <v>0.1024453007910956</v>
@@ -6405,28 +6405,28 @@
         <v>0.01455079123504026</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.01132274874581185</v>
+        <v>0.01132274874581184</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008118296457789055</v>
+        <v>0.008118296457789054</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.00494361855388884</v>
+        <v>0.004943618553888839</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>24419.77128613649</v>
+        <v>24419.77128613648</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>3512.981078027557</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2768.053604727735</v>
+        <v>2768.053604727734</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>2010.698402382618</v>
+        <v>2010.698402382617</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1245.763044370075</v>
+        <v>1245.763044370074</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6442,7 +6442,7 @@
         <v>0.02940634731723226</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.02572933705455119</v>
+        <v>0.02572933705455118</v>
       </c>
       <c r="F58" s="156" t="n">
         <v>0.01783692681688848</v>
@@ -6454,7 +6454,7 @@
         <v>0.1285217416662355</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.00195614948044026</v>
+        <v>0.001956149480440259</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0.001530714831127044</v>
@@ -6463,13 +6463,13 @@
         <v>0.001112151418622067</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.0006921598570196272</v>
+        <v>0.0006921598570196271</v>
       </c>
       <c r="M58" s="158" t="n">
         <v>34870.49269478698</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>535.0111726461538</v>
+        <v>535.0111726461537</v>
       </c>
       <c r="O58" s="159" t="n">
         <v>421.8956008204515</v>
@@ -6489,7 +6489,7 @@
         <v>1.859810032859678</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.03498090547053462</v>
+        <v>0.03498090547053461</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0.03060684476093885</v>
@@ -6498,7 +6498,7 @@
         <v>0.0212182711485823</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.01246972906807083</v>
+        <v>0.01246972906807082</v>
       </c>
       <c r="Y58" s="155" t="n">
         <v>0.1344158608758302</v>
@@ -6507,19 +6507,19 @@
         <v>0.002041645422390707</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.001596143027367506</v>
+        <v>0.001596143027367505</v>
       </c>
       <c r="AB58" s="156" t="n">
         <v>0.001160123869262823</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0007223649134025066</v>
+        <v>0.0007223649134025065</v>
       </c>
       <c r="AD58" s="158" t="n">
         <v>34870.49269478698</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>535.0111726461538</v>
+        <v>535.0111726461537</v>
       </c>
       <c r="AF58" s="159" t="n">
         <v>421.8956008204515</v>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.7721575165614206</v>
+        <v>0.7721575165614205</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.05678907987068529</v>
+        <v>0.05678907987068528</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.04612758969311258</v>
+        <v>0.04612758969311257</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.03178425633205065</v>
@@ -6556,28 +6556,28 @@
         <v>0.1045534871842442</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007063546815800388</v>
+        <v>0.007063546815800387</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.005509581950653443</v>
+        <v>0.005509581950653442</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.003965738058900082</v>
+        <v>0.003965738058900081</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.002428689148766428</v>
+        <v>0.002428689148766427</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>59290.26398092346</v>
+        <v>59290.26398092345</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>4047.992250673711</v>
+        <v>4047.99225067371</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>3189.949205548186</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2319.354396052147</v>
+        <v>2319.354396052146</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>1439.636536560427</v>
@@ -6588,19 +6588,19 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.9405321546448954</v>
+        <v>0.9405321546448953</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.06925470936499309</v>
+        <v>0.06925470936499308</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.05628742049200187</v>
+        <v>0.05628742049200185</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.03878486359605263</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.02299065583378187</v>
+        <v>0.02299065583378186</v>
       </c>
       <c r="Y59" s="161" t="n">
         <v>0.119106662014483</v>
@@ -6609,25 +6609,25 @@
         <v>0.008040059697795972</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006269674174468265</v>
+        <v>0.006269674174468263</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004514740694604596</v>
+        <v>0.004514740694604595</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.002766502879534259</v>
+        <v>0.002766502879534258</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>59290.26398092346</v>
+        <v>59290.26398092345</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>4047.992250673711</v>
+        <v>4047.99225067371</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>3189.949205548186</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2319.354396052147</v>
+        <v>2319.354396052146</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>1439.636536560427</v>
@@ -6745,40 +6745,40 @@
         <v>0.780250342278563</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.05653949674813941</v>
+        <v>0.0565394967481394</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.04592564622401284</v>
+        <v>0.04592564622401283</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.03164108993301992</v>
+        <v>0.03164108993301991</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.01875470868914996</v>
+        <v>0.01875470868914995</v>
       </c>
       <c r="H61" s="161" t="n">
         <v>0.1053570635198703</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007011119904813965</v>
+        <v>0.007011119904813964</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005468726820778082</v>
+        <v>0.00546872682077808</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>0.003936378011077712</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.002410774480896692</v>
+        <v>0.002410774480896691</v>
       </c>
       <c r="M61" s="164" t="n">
         <v>60194.48366272544</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>4048.101158684235</v>
+        <v>4048.101158684234</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885116</v>
       </c>
       <c r="P61" s="165" t="n">
         <v>2319.448089110551</v>
@@ -6795,16 +6795,16 @@
         <v>0.9495378173707681</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.06889174216425434</v>
+        <v>0.06889174216425432</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.05599332250475067</v>
+        <v>0.05599332250475066</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.03857631211072682</v>
+        <v>0.03857631211072681</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.02286050952639389</v>
+        <v>0.02286050952639388</v>
       </c>
       <c r="Y61" s="161" t="n">
         <v>0.1199133003188764</v>
@@ -6813,22 +6813,22 @@
         <v>0.007973203080319223</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006217595835888402</v>
+        <v>0.0062175958358884</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.004477280597217065</v>
+        <v>0.004477280597217064</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.002743613984729004</v>
+        <v>0.002743613984729003</v>
       </c>
       <c r="AD61" s="164" t="n">
         <v>60194.48366272544</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>4048.101158684235</v>
+        <v>4048.101158684234</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885116</v>
       </c>
       <c r="AG61" s="165" t="n">
         <v>2319.448089110551</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="C62" s="155" t="n">
-        <v>2.343143258645737</v>
+        <v>2.343143258645736</v>
       </c>
       <c r="D62" s="156" t="n">
-        <v>0.007332213935871515</v>
+        <v>0.007332213935871513</v>
       </c>
       <c r="E62" s="156" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="155" t="n">
-        <v>2.05014717978564</v>
+        <v>2.050147179785639</v>
       </c>
       <c r="I62" s="156" t="n">
-        <v>0.006454793054520391</v>
+        <v>0.006454793054520389</v>
       </c>
       <c r="J62" s="156" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="158" t="n">
-        <v>18889.36835995101</v>
+        <v>18889.368359951</v>
       </c>
       <c r="N62" s="159" t="n">
-        <v>66.64626502818014</v>
+        <v>66.64626502818012</v>
       </c>
       <c r="O62" s="159" t="n">
         <v>0</v>
@@ -6897,7 +6897,7 @@
         <v>1.5291790088134</v>
       </c>
       <c r="U62" s="156" t="n">
-        <v>0.004785139618541352</v>
+        <v>0.004785139618541351</v>
       </c>
       <c r="V62" s="156" t="n">
         <v>0</v>
@@ -6912,7 +6912,7 @@
         <v>1.344132587536297</v>
       </c>
       <c r="Z62" s="156" t="n">
-        <v>0.004231100087015822</v>
+        <v>0.004231100087015821</v>
       </c>
       <c r="AA62" s="156" t="n">
         <v>0</v>
@@ -6924,10 +6924,10 @@
         <v>0</v>
       </c>
       <c r="AD62" s="158" t="n">
-        <v>18889.36835995101</v>
+        <v>18889.368359951</v>
       </c>
       <c r="AE62" s="159" t="n">
-        <v>66.64626502818014</v>
+        <v>66.64626502818012</v>
       </c>
       <c r="AF62" s="159" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>0.05099623940146895</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.04001989393006469</v>
+        <v>0.04001989393006468</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0273131440004346</v>
@@ -6964,25 +6964,25 @@
         <v>0.1362219250488082</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.007001346140073273</v>
+        <v>0.007001346140073271</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005361791333567501</v>
+        <v>0.005361791333567499</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.003850803170851695</v>
+        <v>0.003850803170851694</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002352466238998582</v>
+        <v>0.002352466238998581</v>
       </c>
       <c r="M63" s="182" t="n">
         <v>79083.85202267645</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>4114.747423712415</v>
+        <v>4114.747423712414</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885116</v>
       </c>
       <c r="P63" s="183" t="n">
         <v>2319.448089110551</v>
@@ -6999,40 +6999,40 @@
         <v>1.044065324748932</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.0566082812078522</v>
+        <v>0.05660828120785219</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.04389258305197666</v>
+        <v>0.04389258305197665</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.02976523137129887</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.01728770672244988</v>
+        <v>0.01728770672244987</v>
       </c>
       <c r="Y63" s="185" t="n">
         <v>0.1532524142210018</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.007860599872847644</v>
+        <v>0.007860599872847642</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006009701722761112</v>
+        <v>0.006009701722761111</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.004311005276815035</v>
+        <v>0.004311005276815034</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.00263036009025719</v>
+        <v>0.002630360090257189</v>
       </c>
       <c r="AD63" s="188" t="n">
         <v>79083.85202267645</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>4114.747423712415</v>
+        <v>4114.747423712414</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885116</v>
       </c>
       <c r="AG63" s="189" t="n">
         <v>2319.448089110551</v>
@@ -7303,13 +7303,13 @@
         <v>1.072741376113453</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>1.349020985944959</v>
+        <v>1.349020985944958</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.6734473024225881</v>
+        <v>0.6734473024225879</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.6979040574879253</v>
+        <v>0.6979040574879249</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.2070345988141619</v>
@@ -7318,7 +7318,7 @@
         <v>0.1900965134390831</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.2346071417436318</v>
+        <v>0.2346071417436317</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.1219881823523848</v>
@@ -7327,19 +7327,19 @@
         <v>0.1292458671683467</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>61232.73873833254</v>
+        <v>61232.73873833253</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>56949.0960418696</v>
+        <v>56949.09604186958</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>71170.91319251488</v>
+        <v>71170.91319251485</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>37489.11030063114</v>
+        <v>37489.11030063112</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>40410.4627293431</v>
+        <v>40410.46272934308</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7353,43 +7353,43 @@
         <v>1.319597643924709</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>1.659453950688004</v>
+        <v>1.659453950688003</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.828419126335919</v>
+        <v>0.8284191263359186</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.8585038019910969</v>
+        <v>0.8585038019910965</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.2568822723524991</v>
+        <v>0.256882272352499</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.2358835385457781</v>
+        <v>0.235883538545778</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.2911252754326971</v>
+        <v>0.2911252754326969</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.1513641782370911</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.1603626903389405</v>
+        <v>0.1603626903389404</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>61232.73873833254</v>
+        <v>61232.73873833253</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>56949.0960418696</v>
+        <v>56949.09604186958</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>71170.91319251488</v>
+        <v>71170.91319251485</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>37489.11030063114</v>
+        <v>37489.11030063112</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>40410.4627293431</v>
+        <v>40410.46272934308</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7408,7 +7408,7 @@
         <v>3.973443174630005</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>0.8115646454014094</v>
+        <v>0.8115646454014093</v>
       </c>
       <c r="G69" s="157" t="n">
         <v>0.8946734527412963</v>
@@ -7420,10 +7420,10 @@
         <v>0.1841755351275582</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.236391959308987</v>
+        <v>0.2363919593089869</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.05060192156151602</v>
+        <v>0.05060192156151601</v>
       </c>
       <c r="L69" s="157" t="n">
         <v>0.0590750238813058</v>
@@ -7435,7 +7435,7 @@
         <v>50372.41274585562</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>65154.34859173407</v>
+        <v>65154.34859173406</v>
       </c>
       <c r="P69" s="159" t="n">
         <v>14043.57906633647</v>
@@ -7458,22 +7458,22 @@
         <v>4.726688377336196</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>0.9654128694650356</v>
+        <v>0.9654128694650355</v>
       </c>
       <c r="X69" s="157" t="n">
         <v>1.064276604629512</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.2451735224054606</v>
+        <v>0.2451735224054605</v>
       </c>
       <c r="Z69" s="156" t="n">
         <v>0.1922251555770212</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.2464961924351191</v>
+        <v>0.246496192435119</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.05278462631177823</v>
+        <v>0.05278462631177822</v>
       </c>
       <c r="AC69" s="157" t="n">
         <v>0.06165298966342742</v>
@@ -7485,7 +7485,7 @@
         <v>50372.41274585562</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>65154.34859173407</v>
+        <v>65154.34859173406</v>
       </c>
       <c r="AG69" s="159" t="n">
         <v>14043.57906633647</v>
@@ -7507,13 +7507,13 @@
         <v>1.505608053813402</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.971302781076527</v>
+        <v>1.971302781076526</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.7062000577003731</v>
+        <v>0.7062000577003729</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.7455394671431665</v>
+        <v>0.7455394671431663</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.2201384343941397</v>
@@ -7525,10 +7525,10 @@
         <v>0.2354567904837624</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.08811294550238463</v>
+        <v>0.08811294550238459</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.09608790793676883</v>
+        <v>0.0960879079367688</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>124836.2559593578</v>
@@ -7537,13 +7537,13 @@
         <v>107321.5087877252</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>136325.261784249</v>
+        <v>136325.2617842489</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>51532.68936696761</v>
+        <v>51532.68936696759</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>56957.33563008178</v>
+        <v>56957.33563008177</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7560,22 +7560,22 @@
         <v>2.405492012344941</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.8617433934363923</v>
+        <v>0.8617433934363919</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.9095952120033229</v>
+        <v>0.9095952120033227</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.2507802925365409</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.2131603234584349</v>
+        <v>0.2131603234584348</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>0.2679399946713101</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.1003109874814644</v>
+        <v>0.1003109874814643</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.1094530661243791</v>
@@ -7587,13 +7587,13 @@
         <v>107321.5087877252</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>136325.261784249</v>
+        <v>136325.2617842489</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>51532.68936696761</v>
+        <v>51532.68936696759</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>56957.33563008178</v>
+        <v>56957.33563008177</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7711,28 +7711,28 @@
         <v>1.512271824941498</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>1.98030566721099</v>
+        <v>1.980305667210989</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.7188648265700477</v>
+        <v>0.7188648265700475</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.7605895278229673</v>
+        <v>0.7605895278229671</v>
       </c>
       <c r="H72" s="161" t="n">
         <v>0.2208725353916684</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.187527652404964</v>
+        <v>0.1875276524049639</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.2358105243155641</v>
+        <v>0.235810524315564</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.08943192861679819</v>
+        <v>0.08943192861679816</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.09776797147340713</v>
+        <v>0.0977679714734071</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>126192.8510438319</v>
@@ -7744,10 +7744,10 @@
         <v>137554.3888828797</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>52696.34048151597</v>
+        <v>52696.34048151596</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>58387.39055912911</v>
+        <v>58387.3905591291</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7761,16 +7761,16 @@
         <v>1.842659497134001</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>2.414422071303447</v>
+        <v>2.414422071303446</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.8764285292919087</v>
+        <v>0.8764285292919085</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.927098598792496</v>
+        <v>0.9270985987924958</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.2513885048022207</v>
+        <v>0.2513885048022206</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.2132606596520567</v>
@@ -7782,7 +7782,7 @@
         <v>0.1017208808810682</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.1112661412000905</v>
+        <v>0.1112661412000904</v>
       </c>
       <c r="AD72" s="164" t="n">
         <v>126192.8510438319</v>
@@ -7794,10 +7794,10 @@
         <v>137554.3888828797</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>52696.34048151597</v>
+        <v>52696.34048151596</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>58387.39055912911</v>
+        <v>58387.3905591291</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,28 +7807,28 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>53.60907303027515</v>
+        <v>53.60907303027513</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>67.6260256079652</v>
+        <v>67.62602560796519</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>19.33166872100499</v>
+        <v>19.33166872100498</v>
       </c>
       <c r="F73" s="156" t="n">
         <v>20.95140155930896</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>22.61989492637709</v>
+        <v>22.61989492637708</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>46.90557842693045</v>
+        <v>46.90557842693043</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>59.53345118089869</v>
+        <v>59.53345118089868</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>17.03286278560236</v>
+        <v>17.03286278560235</v>
       </c>
       <c r="K73" s="156" t="n">
         <v>18.58548072111209</v>
@@ -7837,10 +7837,10 @@
         <v>20.24652483881341</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>432172.2644007935</v>
+        <v>432172.2644007934</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>614687.7416411932</v>
+        <v>614687.741641193</v>
       </c>
       <c r="O73" s="159" t="n">
         <v>198157.6575402865</v>
@@ -7849,7 +7849,7 @@
         <v>243364.0560568464</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>299695.0017220364</v>
+        <v>299695.0017220363</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>34.98628129430804</v>
+        <v>34.98628129430803</v>
       </c>
       <c r="U73" s="156" t="n">
         <v>44.134006073938</v>
@@ -7872,7 +7872,7 @@
         <v>14.76216546954642</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>30.75258065495029</v>
+        <v>30.75258065495028</v>
       </c>
       <c r="Z73" s="156" t="n">
         <v>39.02402266722537</v>
@@ -7881,16 +7881,16 @@
         <v>11.16468761072311</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>12.17970731203275</v>
+        <v>12.17970731203274</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>13.26433621921414</v>
+        <v>13.26433621921413</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>432172.2644007935</v>
+        <v>432172.2644007934</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>614687.7416411932</v>
+        <v>614687.741641193</v>
       </c>
       <c r="AF73" s="159" t="n">
         <v>198157.6575402865</v>
@@ -7899,7 +7899,7 @@
         <v>243364.0560568464</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>299695.0017220364</v>
+        <v>299695.0017220363</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>6.552873190447237</v>
+        <v>6.552873190447235</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>8.960062688986913</v>
+        <v>8.960062688986911</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>4.211582972667646</v>
@@ -7921,34 +7921,34 @@
         <v>3.486320854276573</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>3.97802386096829</v>
+        <v>3.978023860968289</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.9617838403237748</v>
+        <v>0.9617838403237747</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>1.230139733020118</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.5642600933153782</v>
+        <v>0.5642600933153781</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.4915265485379859</v>
+        <v>0.4915265485379858</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.5850962548431877</v>
+        <v>0.5850962548431876</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>558365.1154446254</v>
+        <v>558365.1154446253</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>722963.0125383056</v>
+        <v>722963.0125383055</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>335712.0464231662</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>296060.3965383624</v>
+        <v>296060.3965383623</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>358082.3922811655</v>
@@ -7959,19 +7959,19 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>7.371538445269556</v>
+        <v>7.371538445269553</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>9.94610101237279</v>
+        <v>9.946101012372788</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>4.619134066950452</v>
+        <v>4.619134066950451</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>3.799311674279436</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>4.2997311886774</v>
+        <v>4.299731188677399</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>1.082026226215444</v>
@@ -7980,25 +7980,25 @@
         <v>1.381111008584069</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.6324443910476704</v>
+        <v>0.6324443910476703</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.5502679442255882</v>
+        <v>0.5502679442255881</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.6542129328723593</v>
+        <v>0.6542129328723592</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>558365.1154446254</v>
+        <v>558365.1154446253</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>722963.0125383056</v>
+        <v>722963.0125383055</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>335712.0464231662</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>296060.3965383624</v>
+        <v>296060.3965383623</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>358082.3922811655</v>
@@ -8260,34 +8260,34 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>222.6082171202979</v>
+        <v>222.6082171202978</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>257.1762540061331</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>292.1642801895782</v>
+        <v>292.1642801895781</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>320.7007119048811</v>
+        <v>320.700711904881</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>342.1348723613769</v>
+        <v>342.1348723613768</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>41.00609317615556</v>
+        <v>41.00609317615555</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>45.57324842173283</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>50.81005218525132</v>
+        <v>50.81005218525131</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>58.09169742555951</v>
+        <v>58.09169742555949</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>63.36045448144259</v>
+        <v>63.36045448144257</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>12127998.91668879</v>
@@ -8296,10 +8296,10 @@
         <v>13652829.57775516</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>15413843.69848081</v>
+        <v>15413843.6984808</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>17852598.59062992</v>
+        <v>17852598.59062991</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>19810500.25376473</v>
@@ -8310,34 +8310,34 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>273.8342021396571</v>
+        <v>273.834202139657</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>316.3569397214936</v>
+        <v>316.3569397214935</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>359.3963133723215</v>
+        <v>359.3963133723213</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>394.4994695440001</v>
+        <v>394.4994695439999</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>420.8659995089119</v>
+        <v>420.8659995089117</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>50.87912095719046</v>
+        <v>50.87912095719044</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.55011186824841</v>
+        <v>56.5501118682484</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>63.05046950934313</v>
+        <v>63.05046950934311</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>72.08076941270744</v>
+        <v>72.08076941270741</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>78.61491562053236</v>
+        <v>78.61491562053233</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>12127998.91668879</v>
@@ -8346,10 +8346,10 @@
         <v>13652829.57775516</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>15413843.69848081</v>
+        <v>15413843.6984808</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>17852598.59062992</v>
+        <v>17852598.59062991</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>19810500.25376473</v>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>304.4930117058337</v>
+        <v>304.4930117058336</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>347.3800017063943</v>
+        <v>347.3800017063942</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>425.7087797595168</v>
@@ -8377,31 +8377,31 @@
         <v>482.532320738689</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>25.03083343969871</v>
+        <v>25.0308334396987</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>23.10818145901084</v>
+        <v>23.10818145901083</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>25.32668220472561</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>28.93376264150738</v>
+        <v>28.93376264150737</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>31.86146664327442</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>6791360.615623762</v>
+        <v>6791360.61562376</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>6320138.304217424</v>
+        <v>6320138.304217423</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>6980539.802886716</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>8030003.027625098</v>
+        <v>8030003.027625097</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>8924374.538327036</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>362.2157197564746</v>
+        <v>362.2157197564745</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>413.2327919191989</v>
@@ -8427,7 +8427,7 @@
         <v>574.0059217877207</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>26.17876930094959</v>
+        <v>26.17876930094958</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>24.11815322259782</v>
@@ -8436,22 +8436,22 @@
         <v>26.40923468263589</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>30.18181526899115</v>
+        <v>30.18181526899114</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>33.25186423227249</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>6791360.615623762</v>
+        <v>6791360.61562376</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>6320138.304217424</v>
+        <v>6320138.304217423</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>6980539.802886716</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>8030003.027625098</v>
+        <v>8030003.027625097</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>8924374.538327036</v>
@@ -8464,34 +8464,34 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>246.393331561206</v>
+        <v>246.3933315612059</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>280.199762762688</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>323.829273451949</v>
+        <v>323.8292734519489</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>354.6932050467334</v>
+        <v>354.6932050467333</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>376.1233387048963</v>
+        <v>376.1233387048962</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>33.36272908199893</v>
+        <v>33.36272908199891</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>34.85184381499515</v>
+        <v>34.85184381499514</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>38.67888896805883</v>
+        <v>38.67888896805881</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>44.25525416709754</v>
+        <v>44.25525416709752</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>48.47617910938312</v>
+        <v>48.47617910938311</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>18919359.53231255</v>
@@ -8503,10 +8503,10 @@
         <v>22394383.50136752</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>25882601.61825502</v>
+        <v>25882601.618255</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>28734874.79209177</v>
+        <v>28734874.79209176</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,34 +8514,34 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>300.1212136810968</v>
+        <v>300.1212136810967</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>341.7057148743657</v>
+        <v>341.7057148743656</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>395.1542797635252</v>
+        <v>395.154279763525</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>432.8157762279388</v>
+        <v>432.8157762279386</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>458.8891709779601</v>
+        <v>458.88917097796</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>38.00660698813338</v>
+        <v>38.00660698813337</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>39.6700003777169</v>
+        <v>39.67000037771689</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>44.01496037850977</v>
+        <v>44.01496037850976</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>50.3817937470335</v>
+        <v>50.38179374703348</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>55.21887770736053</v>
+        <v>55.21887770736051</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>18919359.53231255</v>
@@ -8553,10 +8553,10 @@
         <v>22394383.50136752</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>25882601.61825502</v>
+        <v>25882601.618255</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>28734874.79209177</v>
+        <v>28734874.79209176</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8668,34 +8668,34 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>247.7627764566513</v>
+        <v>247.7627764566512</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>281.7396010690288</v>
+        <v>281.7396010690287</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>325.6164487905561</v>
+        <v>325.616448790556</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>356.7356820802004</v>
+        <v>356.7356820802002</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>378.4495602999132</v>
+        <v>378.4495602999131</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>33.45536318609318</v>
+        <v>33.45536318609317</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>34.93681830647735</v>
+        <v>34.93681830647734</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>38.77370387128838</v>
+        <v>38.77370387128836</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>44.38047164873011</v>
+        <v>44.38047164873009</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>48.64679891324702</v>
+        <v>48.646798913247</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>19114317.02304444</v>
@@ -8704,13 +8704,13 @@
         <v>20171923.54249777</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>22617706.12749873</v>
+        <v>22617706.12749872</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>26150486.53096438</v>
+        <v>26150486.53096437</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>29052046.44009361</v>
+        <v>29052046.4400936</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,34 +8718,34 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>301.518773186745</v>
+        <v>301.5187731867449</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>343.2915584793586</v>
+        <v>343.2915584793585</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>396.9970665420536</v>
+        <v>396.9970665420535</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>434.9264529790294</v>
+        <v>434.9264529790292</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>461.3001418412258</v>
+        <v>461.3001418412257</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>38.07758947509446</v>
+        <v>38.07758947509445</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>39.7309347321952</v>
+        <v>39.73093473219519</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>44.08324416866598</v>
+        <v>44.08324416866597</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>50.47884731827361</v>
+        <v>50.47884731827359</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>55.3631369787192</v>
+        <v>55.36313697871919</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>19114317.02304444</v>
@@ -8754,13 +8754,13 @@
         <v>20171923.54249777</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>22617706.12749873</v>
+        <v>22617706.12749872</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>26150486.53096438</v>
+        <v>26150486.53096437</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>29052046.44009361</v>
+        <v>29052046.4400936</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,43 +8770,43 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>977.4180842620627</v>
+        <v>977.4180842620624</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>1019.233029543745</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>898.5105926452326</v>
+        <v>898.5105926452325</v>
       </c>
       <c r="F84" s="156" t="n">
         <v>939.7454315634828</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>982.1007605353429</v>
+        <v>982.1007605353426</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>855.1977867881255</v>
+        <v>855.1977867881252</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>897.2649103772727</v>
+        <v>897.2649103772725</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>791.665109557127</v>
+        <v>791.6651095571269</v>
       </c>
       <c r="K84" s="156" t="n">
         <v>833.6254045646929</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>879.0548102506638</v>
+        <v>879.0548102506635</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>7879505.517718391</v>
+        <v>7879505.51771839</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9264333.420513242</v>
+        <v>9264333.420513241</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>9210107.874456571</v>
+        <v>9210107.87445657</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>10915749.91958313</v>
@@ -8820,43 +8820,43 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>637.8812783952496</v>
+        <v>637.8812783952494</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>665.1704918667241</v>
+        <v>665.170491866724</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>586.384777115035</v>
+        <v>586.3847771150349</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>613.2954023501453</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>640.9372803002749</v>
+        <v>640.9372803002747</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>560.6910690826734</v>
+        <v>560.6910690826733</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>588.154818955014</v>
+        <v>588.1548189550139</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>518.9200284044698</v>
+        <v>518.9200284044697</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>546.3035144385174</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>575.9051813143479</v>
+        <v>575.9051813143477</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>7879505.517718391</v>
+        <v>7879505.51771839</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9264333.420513242</v>
+        <v>9264333.420513241</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>9210107.874456571</v>
+        <v>9210107.87445657</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>10915749.91958313</v>
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>316.7946763547364</v>
+        <v>316.7946763547362</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>364.8190891421732</v>
+        <v>364.8190891421731</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>399.2870703808555</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>436.4811863999034</v>
+        <v>436.4811863999033</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>467.2999634335059</v>
+        <v>467.2999634335058</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>46.49685589258146</v>
+        <v>46.49685589258145</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>50.08653092010205</v>
+        <v>50.08653092010204</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>53.49574282517764</v>
+        <v>53.49574282517762</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>61.53825193390818</v>
+        <v>61.53825193390817</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>68.73147775105373</v>
+        <v>68.73147775105372</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>26993822.54076284</v>
+        <v>26993822.54076283</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>29436256.96301101</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>31827814.0019553</v>
+        <v>31827814.00195529</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>37066236.45054751</v>
+        <v>37066236.4505475</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>42064073.68769295</v>
+        <v>42064073.68769294</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>356.3725511139156</v>
+        <v>356.3725511139154</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>404.9667550105227</v>
+        <v>404.9667550105225</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>437.9257208651933</v>
+        <v>437.9257208651932</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>475.667081834498</v>
+        <v>475.6670818344978</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>505.0910445654742</v>
+        <v>505.0910445654739</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>52.30990104324961</v>
+        <v>52.30990104324959</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>56.2334972025556</v>
+        <v>56.23349720255558</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>59.96008382574408</v>
+        <v>59.96008382574406</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>68.89257046975366</v>
+        <v>68.89257046975364</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>76.85063998951642</v>
+        <v>76.8506399895164</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>26993822.54076283</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>29436256.96301101</v>
+        <v>29436256.963011</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>31827814.0019553</v>
+        <v>31827814.00195529</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>37066236.45054752</v>
+        <v>37066236.4505475</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>42064073.68769296</v>
+        <v>42064073.68769294</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="C95" s="79" t="n">
-        <v>8061.550778106699</v>
+        <v>8061.5507781067</v>
       </c>
       <c r="D95" s="80" t="n">
         <v>9089.514519226654</v>
@@ -9898,7 +9898,7 @@
         <v>1553.115988492877</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>9213.664534038991</v>
+        <v>9213.664534038993</v>
       </c>
       <c r="N95" s="80" t="n">
         <v>10325.08160451507</v>
@@ -9960,7 +9960,7 @@
         <v>19981.10872635</v>
       </c>
       <c r="AH95" s="81" t="n">
-        <v>22594.04441874078</v>
+        <v>22594.04441874079</v>
       </c>
       <c r="AJ95" s="120" t="n">
         <v>45.96865203761755</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>75746.07656057712</v>
+        <v>75746.07656057713</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>72688.08266062764</v>
@@ -10050,7 +10050,7 @@
         <v>77924.74582767999</v>
       </c>
       <c r="X96" s="137" t="n">
-        <v>83280.18114809449</v>
+        <v>83280.1811480945</v>
       </c>
       <c r="Y96" s="135" t="n">
         <v>440290.5054708906</v>
@@ -10068,7 +10068,7 @@
         <v>464068.2038937364</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>516036.5820314677</v>
+        <v>516036.5820314678</v>
       </c>
       <c r="AE96" s="136" t="n">
         <v>523464.8106088847</v>
